--- a/data/events/data.xlsx
+++ b/data/events/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ivpf201v.takamatsu.local\Profile\n11601\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D803A455-051A-44D4-8A35-7F6DFD4012F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39C28AAB-3ED5-4ED2-AFA1-3208AC2CB52A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{65C98C61-441D-42E5-BB0B-962E7C1AD80E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3E6A740E-A444-4334-A36B-E4E3ACB89794}"/>
   </bookViews>
   <sheets>
     <sheet name="オープンデータ" sheetId="1" r:id="rId1"/>
@@ -3034,7 +3034,7 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>10月6日（火）16：00まで</t>
+    <t>10月8日（木）16：00まで</t>
     <rPh sb="2" eb="3">
       <t>ガツ</t>
     </rPh>
@@ -3042,7 +3042,7 @@
       <t>ニチ</t>
     </rPh>
     <rPh sb="6" eb="7">
-      <t>カ</t>
+      <t>モク</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -4344,7 +4344,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A743260-2D34-4782-A611-2E65DD7F1AB0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29E1B6BD-D7CB-46B5-8C6C-EC1B2CD8F5B7}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -6233,10 +6233,10 @@
         <v>46307</v>
       </c>
       <c r="D38" s="19">
-        <v>0.41666666666666669</v>
+        <v>0.5625</v>
       </c>
       <c r="E38" s="19">
-        <v>0.5</v>
+        <v>0.64583333333333337</v>
       </c>
       <c r="F38" s="7" t="s">
         <v>299</v>
@@ -6630,25 +6630,25 @@
   </autoFilter>
   <phoneticPr fontId="2"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B15:B16" xr:uid="{22682D05-A295-45DE-91AB-0694ABA2F72B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B15:B16" xr:uid="{18503AD5-AD28-4B21-8657-836C82F8F819}">
       <formula1>$V$2:$V$2</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B17:B1048576 B2:B14" xr:uid="{6723799D-DE28-4DF4-98F2-7A7A3CBE2C1A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B17:B1048576 B2:B14" xr:uid="{244C7026-6D61-4F49-9840-71CD34F1E8BA}">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="N14" r:id="rId1" display="https://www.city.takamatsu.kagawa.jp/kurashi/kosodate/bunka/maizobunkazai/bunzai_up20250526102.html" xr:uid="{D1972188-ACB4-4BF7-B00E-786DD0D2F812}"/>
-    <hyperlink ref="N41" r:id="rId2" xr:uid="{5A5E756A-F014-467C-BDF6-1F821971C426}"/>
-    <hyperlink ref="N45" r:id="rId3" xr:uid="{72EFD0A6-4C76-4002-9948-58328F08F005}"/>
-    <hyperlink ref="N32" r:id="rId4" xr:uid="{9E7DF1B0-6ED8-4863-BE42-DB4B51A3E187}"/>
-    <hyperlink ref="N5" display="https://www.flat-takamatsu.net/bcs/info8723.html" xr:uid="{8326DC66-07BD-45E6-9A6D-160E860A8C38}"/>
-    <hyperlink ref="N20" display="https://www.flat-takamatsu.net/bcs/info8699.html" xr:uid="{8EE8F76A-7BB1-4E8C-865E-BBD66C0D94A1}"/>
-    <hyperlink ref="N37" display="https://www.flat-takamatsu.net/bcs/info8760.html" xr:uid="{E1FB1149-4CA2-48F1-A24B-462CEACFAF06}"/>
-    <hyperlink ref="N33" display="https://www.flat-takamatsu.net/bcs/info8759.html" xr:uid="{6E0D43EC-F0CA-4F88-B8B6-AEE04D3A5B0C}"/>
-    <hyperlink ref="N3" r:id="rId5" xr:uid="{5FD75FDC-520F-4474-A6AA-6658EFA25DE8}"/>
-    <hyperlink ref="N15" r:id="rId6" xr:uid="{3E4455BE-8BA3-4B8D-8665-AACB7B9AA108}"/>
-    <hyperlink ref="N17" r:id="rId7" xr:uid="{3AAA1728-1C96-4A51-81D4-CDED4D3F0667}"/>
+    <hyperlink ref="N14" r:id="rId1" display="https://www.city.takamatsu.kagawa.jp/kurashi/kosodate/bunka/maizobunkazai/bunzai_up20250526102.html" xr:uid="{EC569656-C886-46FA-8FDF-9423768B6952}"/>
+    <hyperlink ref="N41" r:id="rId2" xr:uid="{5C049AF0-690C-430F-8437-E92901A318B6}"/>
+    <hyperlink ref="N45" r:id="rId3" xr:uid="{6F68D084-A43C-463A-8849-1BD3FF249A42}"/>
+    <hyperlink ref="N32" r:id="rId4" xr:uid="{A8707D5E-1D2B-4C43-994A-0768C33FCDD6}"/>
+    <hyperlink ref="N5" display="https://www.flat-takamatsu.net/bcs/info8723.html" xr:uid="{A3E6C6BC-B226-43CC-8D86-1B31846827ED}"/>
+    <hyperlink ref="N20" display="https://www.flat-takamatsu.net/bcs/info8699.html" xr:uid="{D7094090-1DEC-4AC9-8678-A42FDDEEC3FB}"/>
+    <hyperlink ref="N37" display="https://www.flat-takamatsu.net/bcs/info8760.html" xr:uid="{2C9C4A8E-2B9F-4BEE-AF13-18AFF8937DFA}"/>
+    <hyperlink ref="N33" display="https://www.flat-takamatsu.net/bcs/info8759.html" xr:uid="{4EE3D1AA-126E-4045-830B-DA72012270C3}"/>
+    <hyperlink ref="N3" r:id="rId5" xr:uid="{B1B3D4AB-F701-4E31-81AB-588D4644889A}"/>
+    <hyperlink ref="N15" r:id="rId6" xr:uid="{0798B693-20EB-4ECB-9575-25137B077EA5}"/>
+    <hyperlink ref="N17" r:id="rId7" xr:uid="{43E7958E-0664-4F36-B221-FF83B3191FB5}"/>
   </hyperlinks>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="43" fitToHeight="0" orientation="landscape" cellComments="asDisplayed" r:id="rId8"/>
